--- a/data/2nd Round/Corrected/Mo_25Se_400Sb_Results Table.xlsx
+++ b/data/2nd Round/Corrected/Mo_25Se_400Sb_Results Table.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -507,6 +506,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,9 +556,6 @@
       <c r="L2" t="n">
         <v>0.00020522</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>14.574</v>
       </c>
@@ -563,6 +569,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S2" t="n">
+        <v>17.30263963630567</v>
+      </c>
+      <c r="T2" t="n">
+        <v>21.40240233133222</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -603,9 +615,6 @@
       <c r="L3" t="n">
         <v>4.858e-05</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>14.553</v>
       </c>
@@ -619,6 +628,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S3" t="n">
+        <v>15.50984322022513</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16.52142328637095</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,9 +674,6 @@
       <c r="L4" t="n">
         <v>7.300999999999999e-05</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>14.558</v>
       </c>
@@ -675,6 +687,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>13.83887299904404</v>
+      </c>
+      <c r="T4" t="n">
+        <v>16.74353619100264</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -715,9 +733,6 @@
       <c r="L5" t="n">
         <v>0.00016364</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>14.826</v>
       </c>
@@ -731,6 +746,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>16.64867687765666</v>
+      </c>
+      <c r="T5" t="n">
+        <v>21.29556759631126</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,9 +792,6 @@
       <c r="L6" t="n">
         <v>0.00033375</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>14.564</v>
       </c>
@@ -787,6 +805,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>18.38757471961808</v>
+      </c>
+      <c r="T6" t="n">
+        <v>34.4583332672113</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -827,9 +851,6 @@
       <c r="L7" t="n">
         <v>0.00061775</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>14.835</v>
       </c>
@@ -843,6 +864,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>18.24114811124268</v>
+      </c>
+      <c r="T7" t="n">
+        <v>53.02842056760274</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -883,9 +910,6 @@
       <c r="L8" t="n">
         <v>0.00017809</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>14.551</v>
       </c>
@@ -899,6 +923,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>17.14553819247429</v>
+      </c>
+      <c r="T8" t="n">
+        <v>22.48728414499361</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -939,9 +969,6 @@
       <c r="L9" t="n">
         <v>0.00029161</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>14.558</v>
       </c>
@@ -955,6 +982,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>16.06788985914918</v>
+      </c>
+      <c r="T9" t="n">
+        <v>25.7161051864319</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -995,9 +1028,6 @@
       <c r="L10" t="n">
         <v>0.00014368</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>14.824</v>
       </c>
@@ -1011,7 +1041,14 @@
           <t>08/21/2026</t>
         </is>
       </c>
-    </row>
+      <c r="S10" t="n">
+        <v>16.5179503614077</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22.96795633974628</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
